--- a/mapping/변수대응표.xlsx
+++ b/mapping/변수대응표.xlsx
@@ -14869,7 +14869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
@@ -14884,8 +14884,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
+      <c r="A1" s="21" t="str">
+        <v>자료 점검 요약</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -14896,8 +14896,8 @@
       <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="33" customHeight="1">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
+      <c r="A2" s="19" t="str">
+        <v>파일 목록, 헤더 및 메타데이터의 점검 결과이다. 수치는 원자료에서 직접 집계하였다.</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
